--- a/Altium-library.xlsx
+++ b/Altium-library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Altium-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94F3AAB-82D7-4DE2-879A-3EC88CEEDFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDBF7BC-F39C-4C32-B8CE-9C1E29141D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="771" activeTab="7" xr2:uid="{C01531D5-0FFE-4276-86E2-3D80C8EFC4F5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="771" firstSheet="1" activeTab="10" xr2:uid="{C01531D5-0FFE-4276-86E2-3D80C8EFC4F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Capacitors_General" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2987" uniqueCount="1062">
   <si>
     <t>Part Number</t>
   </si>
@@ -1795,9 +1795,6 @@
   </si>
   <si>
     <t>SOIC-8</t>
-  </si>
-  <si>
-    <t>ADM6-60-01.5-L-4-2-A-TR</t>
   </si>
   <si>
     <t>CONN 0.635MM HDR 60POS SMD</t>
@@ -3173,6 +3170,75 @@
   </si>
   <si>
     <t>270K</t>
+  </si>
+  <si>
+    <t>OCULINK RECEPTACLE Vertical SMT shell leg DIP length 2.9mm with hold down tape and reel package</t>
+  </si>
+  <si>
+    <t>G14A42221612AHR</t>
+  </si>
+  <si>
+    <t>6-ch, 4.5-V to 5.5-V inverters with TTL-compatible CMOS inputs</t>
+  </si>
+  <si>
+    <t>SN74ACT04PWR</t>
+  </si>
+  <si>
+    <t>TSSOP-14</t>
+  </si>
+  <si>
+    <t>SN74ACT04</t>
+  </si>
+  <si>
+    <t>6-channel buffer with Schmitt-trigger inputs</t>
+  </si>
+  <si>
+    <t>SN74ACT17</t>
+  </si>
+  <si>
+    <t>SN74ACT17PWR</t>
+  </si>
+  <si>
+    <t>1586037-4</t>
+  </si>
+  <si>
+    <t>TE Connectivity / AMP</t>
+  </si>
+  <si>
+    <t>Headers &amp; Wire Housings VERT HDR NO PEGS 4P</t>
+  </si>
+  <si>
+    <t>IHLP2525CZER2R2M01</t>
+  </si>
+  <si>
+    <t>IHLP2525CZER4R7M01</t>
+  </si>
+  <si>
+    <t>IHLP2525CZER1R0M01</t>
+  </si>
+  <si>
+    <t>2.2µH ±20% 8A 20mΩ Shielded SMD Inductor</t>
+  </si>
+  <si>
+    <t>4.7µH ±20% 5.5A 40mΩ Shielded SMD Inductor</t>
+  </si>
+  <si>
+    <t>1.0µH ±20% 11A 10mΩ Shielded SMD Inductor</t>
+  </si>
+  <si>
+    <t>2.2uH</t>
+  </si>
+  <si>
+    <t>4.7uH</t>
+  </si>
+  <si>
+    <t>1.0uH</t>
+  </si>
+  <si>
+    <t>S_Band_Radiator_Niz</t>
+  </si>
+  <si>
+    <t>Керамическая антенна на S_Band</t>
   </si>
 </sst>
 </file>
@@ -4010,10 +4076,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>17</v>
@@ -4054,7 +4120,7 @@
         <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
@@ -4075,7 +4141,7 @@
         <v>33</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>10</v>
@@ -4109,7 +4175,7 @@
         <v>322</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>9</v>
@@ -4130,7 +4196,7 @@
         <v>33</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>10</v>
@@ -4164,7 +4230,7 @@
         <v>61</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -4185,7 +4251,7 @@
         <v>33</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>10</v>
@@ -4219,7 +4285,7 @@
         <v>66</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -4240,7 +4306,7 @@
         <v>33</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>10</v>
@@ -4274,7 +4340,7 @@
         <v>161</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>9</v>
@@ -4295,7 +4361,7 @@
         <v>33</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>10</v>
@@ -4329,7 +4395,7 @@
         <v>153</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>9</v>
@@ -4350,7 +4416,7 @@
         <v>33</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>10</v>
@@ -4405,7 +4471,7 @@
         <v>33</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>10</v>
@@ -4436,7 +4502,7 @@
         <v>153</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>9</v>
@@ -4457,7 +4523,7 @@
         <v>33</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>10</v>
@@ -4491,7 +4557,7 @@
         <v>58</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
@@ -4512,7 +4578,7 @@
         <v>33</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>10</v>
@@ -4546,7 +4612,7 @@
         <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>9</v>
@@ -4567,7 +4633,7 @@
         <v>33</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>10</v>
@@ -4601,7 +4667,7 @@
         <v>168</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>9</v>
@@ -4622,7 +4688,7 @@
         <v>33</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>10</v>
@@ -4656,7 +4722,7 @@
         <v>63</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
@@ -4677,7 +4743,7 @@
         <v>33</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>10</v>
@@ -4723,7 +4789,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>88</v>
@@ -4753,7 +4819,7 @@
         <v>377</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>9</v>
@@ -4774,7 +4840,7 @@
         <v>33</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>10</v>
@@ -4808,7 +4874,7 @@
         <v>164</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>9</v>
@@ -4829,7 +4895,7 @@
         <v>33</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>10</v>
@@ -4863,7 +4929,7 @@
         <v>318</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>9</v>
@@ -4884,7 +4950,7 @@
         <v>33</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>10</v>
@@ -4918,7 +4984,7 @@
         <v>312</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>9</v>
@@ -4939,7 +5005,7 @@
         <v>33</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>10</v>
@@ -4973,7 +5039,7 @@
         <v>417</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>9</v>
@@ -4994,7 +5060,7 @@
         <v>33</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>10</v>
@@ -5046,7 +5112,7 @@
         <v>185</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>88</v>
@@ -5073,7 +5139,7 @@
         <v>411</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>11</v>
@@ -5094,7 +5160,7 @@
         <v>33</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>10</v>
@@ -5122,7 +5188,7 @@
         <v>472</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>9</v>
@@ -5143,7 +5209,7 @@
         <v>33</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>10</v>
@@ -5177,7 +5243,7 @@
         <v>323</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>9</v>
@@ -5198,7 +5264,7 @@
         <v>33</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>10</v>
@@ -5232,7 +5298,7 @@
         <v>473</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>9</v>
@@ -5253,7 +5319,7 @@
         <v>33</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>10</v>
@@ -5287,7 +5353,7 @@
         <v>414</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>9</v>
@@ -5308,7 +5374,7 @@
         <v>33</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>10</v>
@@ -5342,7 +5408,7 @@
         <v>441</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>11</v>
@@ -5363,7 +5429,7 @@
         <v>33</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>10</v>
@@ -5409,7 +5475,7 @@
         <v>185</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>88</v>
@@ -5439,7 +5505,7 @@
         <v>166</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>9</v>
@@ -5460,7 +5526,7 @@
         <v>33</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>10</v>
@@ -5494,7 +5560,7 @@
         <v>523</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D29" s="2">
         <v>1206</v>
@@ -5515,7 +5581,7 @@
         <v>33</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>10</v>
@@ -5543,7 +5609,7 @@
         <v>527</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D30" s="2">
         <v>1210</v>
@@ -5564,7 +5630,7 @@
         <v>33</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>10</v>
@@ -5592,7 +5658,7 @@
         <v>547</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>9</v>
@@ -5613,7 +5679,7 @@
         <v>33</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>10</v>
@@ -5631,7 +5697,7 @@
         <v>31</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="Q31" s="2" t="str">
         <f t="shared" si="3"/>
@@ -5640,13 +5706,13 @@
     </row>
     <row r="32" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>685</v>
-      </c>
       <c r="C32" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>9</v>
@@ -5667,7 +5733,7 @@
         <v>33</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>10</v>
@@ -5695,13 +5761,13 @@
     </row>
     <row r="33" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>721</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>25</v>
@@ -5722,7 +5788,7 @@
         <v>33</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>10</v>
@@ -5737,7 +5803,7 @@
         <v>18</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="P33" s="2" t="str">
         <f t="shared" si="4"/>
@@ -5750,19 +5816,19 @@
     </row>
     <row r="34" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>845</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>846</v>
       </c>
       <c r="F34" s="2">
         <v>16</v>
@@ -5777,7 +5843,7 @@
         <v>33</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>10</v>
@@ -5887,13 +5953,13 @@
         <v>276</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>273</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>287</v>
@@ -5921,13 +5987,13 @@
         <v>280</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>277</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>285</v>
@@ -5955,13 +6021,13 @@
         <v>375</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>372</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>285</v>
@@ -5989,13 +6055,13 @@
         <v>375</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>428</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="K5" s="2" t="str">
         <f>_xlfn.CONCAT("Q-",F5)</f>
@@ -6016,8 +6082,8 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.25" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34" style="13" customWidth="1"/>
+    <col min="1" max="1" width="49" style="13" customWidth="1"/>
+    <col min="2" max="2" width="53.25" style="13" customWidth="1"/>
     <col min="3" max="3" width="33.125" style="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.125" style="13" customWidth="1"/>
     <col min="5" max="5" width="26.5" style="13" bestFit="1" customWidth="1"/>
@@ -6061,7 +6127,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>174</v>
       </c>
@@ -6075,13 +6141,13 @@
         <v>177</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>178</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>177</v>
@@ -6095,7 +6161,7 @@
         <v>D-SS24FL</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>179</v>
       </c>
@@ -6109,13 +6175,13 @@
         <v>181</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>178</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>181</v>
@@ -6129,7 +6195,7 @@
         <v>D-MBRA160T3G</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>216</v>
       </c>
@@ -6137,13 +6203,13 @@
         <v>215</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>216</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>216</v>
@@ -6157,13 +6223,13 @@
         <v>251</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>216</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>250</v>
@@ -6183,13 +6249,13 @@
         <v>285</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>286</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>285</v>
@@ -6217,13 +6283,13 @@
         <v>7050</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>330</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>328</v>
@@ -6251,13 +6317,13 @@
         <v>337</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>334</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>339</v>
@@ -6285,13 +6351,13 @@
         <v>361</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>362</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>361</v>
@@ -6319,7 +6385,7 @@
         <v>448</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>446</v>
@@ -6345,7 +6411,7 @@
         <v>568</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>566</v>
@@ -6362,19 +6428,19 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>590</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>592</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>591</v>
-      </c>
       <c r="E12" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I12" s="17" t="str">
         <f t="shared" si="0"/>
@@ -6387,22 +6453,22 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>597</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="C13" s="13" t="s">
         <v>598</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>599</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I13" s="17" t="str">
         <f t="shared" si="0"/>
@@ -6415,19 +6481,19 @@
     </row>
     <row r="14" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>338</v>
@@ -6443,19 +6509,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
+        <v>604</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>605</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="C15" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>607</v>
-      </c>
       <c r="E15" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I15" s="17" t="str">
         <f t="shared" si="0"/>
@@ -6468,19 +6534,19 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>660</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="C16" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="E16" s="13" t="s">
+        <v>904</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>662</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>905</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>663</v>
       </c>
       <c r="I16" s="17" t="str">
         <f t="shared" si="0"/>
@@ -6493,22 +6559,22 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>176</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I17" s="17" t="str">
         <f t="shared" si="0"/>
@@ -6521,41 +6587,61 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>251</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>216</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
+        <v>680</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>681</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="E19" s="13" t="s">
+        <v>904</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>682</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>905</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>683</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>904</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>900</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>1060</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I24" s="31"/>
@@ -6657,7 +6743,7 @@
         <v>401</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J2" s="2" t="str">
         <f t="shared" ref="J2:J7" si="0">_xlfn.CONCAT("D-",A2)</f>
@@ -6760,13 +6846,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>613</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>576</v>
@@ -6775,7 +6861,7 @@
         <v>405</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -6788,16 +6874,16 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>456</v>
@@ -6806,7 +6892,7 @@
         <v>405</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -6824,13 +6910,13 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{160160A9-941D-465D-A771-2D9949761A38}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23" style="2" customWidth="1"/>
+    <col min="2" max="2" width="73" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="32.625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="20.25" style="2" bestFit="1" customWidth="1"/>
@@ -6891,15 +6977,15 @@
         <v>507</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I2" s="2" t="str">
-        <f t="shared" ref="I2:I13" si="0">_xlfn.CONCAT("D-",A2)</f>
-        <v>D-TXS02612RTWR</v>
+        <f>A2</f>
+        <v>TXS02612RTWR</v>
       </c>
       <c r="J2" s="2" t="str">
         <f>I2</f>
-        <v>D-TXS02612RTWR</v>
+        <v>TXS02612RTWR</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6922,15 +7008,15 @@
         <v>549</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I3" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>D-SN74AVC4T245RSVR</v>
+        <f t="shared" ref="I3:I15" si="0">A3</f>
+        <v>SN74AVC4T245RSVR</v>
       </c>
       <c r="J3" s="2" t="str">
         <f>I3</f>
-        <v>D-SN74AVC4T245RSVR</v>
+        <v>SN74AVC4T245RSVR</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -6953,15 +7039,15 @@
         <v>553</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I4" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-SN74AVC2T245RSW</v>
+        <v>SN74AVC2T245RSW</v>
       </c>
       <c r="J4" s="2" t="str">
         <f t="shared" ref="J4:J9" si="1">I4</f>
-        <v>D-SN74AVC2T245RSW</v>
+        <v>SN74AVC2T245RSW</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6984,15 +7070,15 @@
         <v>555</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I5" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-FT4232HL</v>
+        <v>FT4232HL</v>
       </c>
       <c r="J5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>D-FT4232HL</v>
+        <v>FT4232HL</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -7015,15 +7101,15 @@
         <v>557</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I6" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-TXS0108EPW</v>
+        <v>TXS0108EPW</v>
       </c>
       <c r="J6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>D-TXS0108EPW</v>
+        <v>TXS0108EPW</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -7046,54 +7132,54 @@
         <v>579</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I7" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-93LC56BT/SN</v>
+        <v>93LC56BT/SN</v>
       </c>
       <c r="J7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>D-93LC56BT/SN</v>
+        <v>93LC56BT/SN</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>506</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I8" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-DP83867ISRGZ</v>
+        <v>DP83867ISRGZ</v>
       </c>
       <c r="J8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>D-DP83867ISRGZ</v>
+        <v>DP83867ISRGZ</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>91</v>
@@ -7105,154 +7191,222 @@
         <v>506</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I9" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-MAX3485CSA</v>
+        <v>MAX3485CSA</v>
       </c>
       <c r="J9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>D-MAX3485CSA</v>
+        <v>MAX3485CSA</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>506</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="I10" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-SN74LVC1G14DBVT</v>
+        <v>SN74LVC1G14DBVT</v>
       </c>
       <c r="J10" s="2" t="str">
-        <f>I10</f>
-        <v>D-SN74LVC1G14DBVT</v>
+        <f t="shared" ref="J10:J15" si="2">I10</f>
+        <v>SN74LVC1G14DBVT</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>506</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="I11" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-SN74LVC1G17DBVT</v>
+        <v>SN74LVC1G17DBVT</v>
       </c>
       <c r="J11" s="2" t="str">
-        <f>I11</f>
-        <v>D-SN74LVC1G17DBVT</v>
+        <f t="shared" si="2"/>
+        <v>SN74LVC1G17DBVT</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>506</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I12" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-TXS0104ERGYR</v>
+        <v>TXS0104ERGYR</v>
       </c>
       <c r="J12" s="2" t="str">
-        <f>I12</f>
-        <v>D-TXS0104ERGYR</v>
+        <f t="shared" si="2"/>
+        <v>TXS0104ERGYR</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>862</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>863</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>506</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>865</v>
-      </c>
       <c r="I13" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>D-SN65LVDS1DBVR</v>
+        <v>SN65LVDS1DBVR</v>
       </c>
       <c r="J13" s="2" t="str">
-        <f>I13</f>
-        <v>D-SN65LVDS1DBVR</v>
+        <f t="shared" si="2"/>
+        <v>SN65LVDS1DBVR</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN74ACT04PWR</v>
+      </c>
+      <c r="J14" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>SN74ACT04PWR</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SN74ACT17PWR</v>
+      </c>
+      <c r="J15" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>SN74ACT17PWR</v>
       </c>
     </row>
   </sheetData>
@@ -7301,19 +7455,19 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>916</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>917</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>19</v>
@@ -7369,13 +7523,13 @@
         <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>10</v>
@@ -7393,7 +7547,7 @@
         <v>31</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="S2" s="2" t="str">
         <f>R2</f>
@@ -7408,7 +7562,7 @@
         <v>232</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>9</v>
@@ -7423,17 +7577,17 @@
         <v>26</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>10</v>
@@ -7467,7 +7621,7 @@
         <v>486</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>9</v>
@@ -7482,17 +7636,17 @@
         <v>26</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>10</v>
@@ -7526,7 +7680,7 @@
         <v>547</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>9</v>
@@ -7541,17 +7695,17 @@
         <v>26</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>10</v>
@@ -7579,10 +7733,10 @@
     </row>
     <row r="6" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>883</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>884</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>54</v>
@@ -7604,13 +7758,13 @@
       </c>
       <c r="I6" s="3"/>
       <c r="J6" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>10</v>
@@ -7628,7 +7782,7 @@
         <v>31</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="S6" s="2" t="str">
         <f t="shared" si="1"/>
@@ -7643,7 +7797,7 @@
         <v>68</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
@@ -7662,13 +7816,13 @@
       </c>
       <c r="I7" s="3"/>
       <c r="J7" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>10</v>
@@ -7702,7 +7856,7 @@
         <v>232</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
@@ -7717,17 +7871,17 @@
         <v>26</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>10</v>
@@ -7761,7 +7915,7 @@
         <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -7780,13 +7934,13 @@
       </c>
       <c r="I9" s="3"/>
       <c r="J9" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>10</v>
@@ -7820,7 +7974,7 @@
         <v>69</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>9</v>
@@ -7839,13 +7993,13 @@
       </c>
       <c r="I10" s="3"/>
       <c r="J10" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>10</v>
@@ -7879,7 +8033,7 @@
         <v>168</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>9</v>
@@ -7898,13 +8052,13 @@
       </c>
       <c r="I11" s="3"/>
       <c r="J11" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>10</v>
@@ -7938,7 +8092,7 @@
         <v>323</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>9</v>
@@ -7957,13 +8111,13 @@
       </c>
       <c r="I12" s="3"/>
       <c r="J12" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>10</v>
@@ -7997,7 +8151,7 @@
         <v>473</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>9</v>
@@ -8016,13 +8170,13 @@
       </c>
       <c r="I13" s="3"/>
       <c r="J13" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>10</v>
@@ -8056,7 +8210,7 @@
         <v>486</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>9</v>
@@ -8071,17 +8225,17 @@
         <v>26</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>10</v>
@@ -8115,7 +8269,7 @@
         <v>547</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>9</v>
@@ -8130,17 +8284,17 @@
         <v>26</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>10</v>
@@ -8168,19 +8322,19 @@
     </row>
     <row r="16" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>842</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>843</v>
       </c>
       <c r="F16" s="2">
         <v>50</v>
@@ -8193,13 +8347,13 @@
       </c>
       <c r="I16" s="3"/>
       <c r="J16" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>10</v>
@@ -8227,19 +8381,19 @@
     </row>
     <row r="17" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>486</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F17" s="2">
         <v>50</v>
@@ -8248,17 +8402,17 @@
         <v>26</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>10</v>
@@ -8286,19 +8440,19 @@
     </row>
     <row r="18" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>486</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F18" s="2">
         <v>50</v>
@@ -8311,13 +8465,13 @@
       </c>
       <c r="I18" s="3"/>
       <c r="J18" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>10</v>
@@ -8426,13 +8580,13 @@
         <v>95</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>96</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>97</v>
@@ -8466,13 +8620,13 @@
         <v>5</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>101</v>
@@ -8506,16 +8660,16 @@
         <v>106</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K4" s="2" t="str">
         <f t="shared" si="0"/>
@@ -8546,13 +8700,13 @@
         <v>113</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>114</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>111</v>
@@ -8586,13 +8740,13 @@
         <v>118</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>119</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>200</v>
@@ -8626,13 +8780,13 @@
         <v>124</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>125</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>201</v>
@@ -8666,13 +8820,13 @@
         <v>267</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>263</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>292</v>
@@ -8706,13 +8860,13 @@
         <v>367</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>363</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>365</v>
@@ -8746,13 +8900,13 @@
         <v>409</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>406</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -8783,13 +8937,13 @@
         <v>433</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>430</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -8802,10 +8956,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>91</v>
@@ -8820,16 +8974,16 @@
         <v>439</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>434</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K12" s="2" t="str">
         <f t="shared" si="0"/>
@@ -8860,16 +9014,16 @@
         <v>463</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>460</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -8894,19 +9048,19 @@
         <v>468</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>920</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>464</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -8937,13 +9091,13 @@
         <v>499</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>496</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K15" s="2" t="str">
         <f t="shared" ref="K15:K24" si="2">_xlfn.CONCAT("D-",A15)</f>
@@ -8971,16 +9125,16 @@
         <v>511</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>508</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K16" s="2" t="str">
         <f t="shared" si="2"/>
@@ -8993,31 +9147,31 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>629</v>
-      </c>
       <c r="G17" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K17" s="2" t="str">
         <f t="shared" si="2"/>
@@ -9030,34 +9184,34 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K18" s="2" t="str">
         <f t="shared" si="2"/>
@@ -9070,34 +9224,34 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>499</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K19" s="2" t="str">
         <f t="shared" si="2"/>
@@ -9110,31 +9264,31 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>730</v>
-      </c>
       <c r="G20" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K20" s="2" t="str">
         <f t="shared" si="2"/>
@@ -9147,34 +9301,34 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="18" t="s">
         <v>758</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="G21" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>760</v>
-      </c>
       <c r="I21" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="K21" s="2" t="str">
         <f t="shared" si="2"/>
@@ -9187,34 +9341,34 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="18" t="s">
         <v>787</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="G22" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="I22" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="K22" s="2" t="str">
         <f t="shared" si="2"/>
@@ -9227,34 +9381,34 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>831</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>832</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>833</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K23" s="2" t="str">
         <f t="shared" si="2"/>
@@ -9267,10 +9421,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>91</v>
@@ -9285,16 +9439,16 @@
         <v>439</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>434</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K24" s="2" t="str">
         <f t="shared" si="2"/>
@@ -9389,13 +9543,13 @@
         <v>20</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J2" s="13" t="s">
         <v>9</v>
@@ -9429,13 +9583,13 @@
         <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J3" s="13" t="s">
         <v>12</v>
@@ -9469,13 +9623,13 @@
         <v>20</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J4" s="13" t="s">
         <v>9</v>
@@ -9509,13 +9663,13 @@
         <v>20</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>9</v>
@@ -9549,13 +9703,13 @@
         <v>20</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>9</v>
@@ -9574,7 +9728,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>128</v>
@@ -9589,13 +9743,13 @@
         <v>20</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>9</v>
@@ -9614,7 +9768,7 @@
         <v>154</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>128</v>
@@ -9629,13 +9783,13 @@
         <v>20</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>9</v>
@@ -9669,13 +9823,13 @@
         <v>20</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J9" s="13" t="s">
         <v>9</v>
@@ -9709,13 +9863,13 @@
         <v>20</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J10" s="13" t="s">
         <v>9</v>
@@ -9734,7 +9888,7 @@
         <v>192</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>128</v>
@@ -9749,13 +9903,13 @@
         <v>20</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J11" s="13" t="s">
         <v>9</v>
@@ -9774,7 +9928,7 @@
         <v>307</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>128</v>
@@ -9789,13 +9943,13 @@
         <v>20</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J12" s="13" t="s">
         <v>9</v>
@@ -9829,13 +9983,13 @@
         <v>20</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J13" s="13" t="s">
         <v>9</v>
@@ -9854,7 +10008,7 @@
         <v>158</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>128</v>
@@ -9869,13 +10023,13 @@
         <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>9</v>
@@ -9894,7 +10048,7 @@
         <v>141</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>128</v>
@@ -9909,13 +10063,13 @@
         <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>9</v>
@@ -9949,13 +10103,13 @@
         <v>20</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J16" s="13" t="s">
         <v>9</v>
@@ -9989,13 +10143,13 @@
         <v>20</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J17" s="13" t="s">
         <v>9</v>
@@ -10014,7 +10168,7 @@
         <v>229</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>128</v>
@@ -10029,13 +10183,13 @@
         <v>20</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J18" s="13" t="s">
         <v>9</v>
@@ -10069,13 +10223,13 @@
         <v>20</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J19" s="13" t="s">
         <v>9</v>
@@ -10094,7 +10248,7 @@
         <v>204</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>128</v>
@@ -10109,13 +10263,13 @@
         <v>20</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J20" s="13" t="s">
         <v>9</v>
@@ -10149,13 +10303,13 @@
         <v>20</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J21" s="13" t="s">
         <v>9</v>
@@ -10189,13 +10343,13 @@
         <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>9</v>
@@ -10214,7 +10368,7 @@
         <v>477</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>128</v>
@@ -10229,13 +10383,13 @@
         <v>20</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J23" s="13" t="s">
         <v>9</v>
@@ -10251,10 +10405,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>128</v>
@@ -10263,19 +10417,19 @@
         <v>9</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F24" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J24" s="13" t="s">
         <v>9</v>
@@ -10294,7 +10448,7 @@
         <v>143</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>128</v>
@@ -10309,13 +10463,13 @@
         <v>20</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J25" s="13" t="s">
         <v>9</v>
@@ -10331,10 +10485,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
+        <v>854</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>855</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>856</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>128</v>
@@ -10343,19 +10497,19 @@
         <v>9</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F26" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J26" s="13" t="s">
         <v>9</v>
@@ -10389,13 +10543,13 @@
         <v>20</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>9</v>
@@ -10429,13 +10583,13 @@
         <v>20</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J28" s="13" t="s">
         <v>9</v>
@@ -10469,13 +10623,13 @@
         <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>9</v>
@@ -10491,10 +10645,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
+        <v>761</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>762</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>763</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>128</v>
@@ -10503,19 +10657,19 @@
         <v>9</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F30" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>9</v>
@@ -10534,7 +10688,7 @@
         <v>309</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>128</v>
@@ -10549,13 +10703,13 @@
         <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>9</v>
@@ -10571,10 +10725,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>128</v>
@@ -10583,19 +10737,19 @@
         <v>9</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F32" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J32" s="13" t="s">
         <v>9</v>
@@ -10614,7 +10768,7 @@
         <v>426</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>128</v>
@@ -10629,13 +10783,13 @@
         <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>9</v>
@@ -10669,13 +10823,13 @@
         <v>20</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J34" s="13" t="s">
         <v>9</v>
@@ -10691,10 +10845,10 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>128</v>
@@ -10703,19 +10857,19 @@
         <v>9</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F35" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J35" s="13" t="s">
         <v>9</v>
@@ -10749,13 +10903,13 @@
         <v>20</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J36" s="13" t="s">
         <v>9</v>
@@ -10789,13 +10943,13 @@
         <v>20</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J37" s="13" t="s">
         <v>9</v>
@@ -10829,13 +10983,13 @@
         <v>20</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J38" s="13" t="s">
         <v>9</v>
@@ -10869,13 +11023,13 @@
         <v>20</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J39" s="13" t="s">
         <v>9</v>
@@ -10909,13 +11063,13 @@
         <v>20</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H40" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J40" s="13" t="s">
         <v>9</v>
@@ -10931,10 +11085,10 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
+        <v>592</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>594</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>128</v>
@@ -10943,19 +11097,19 @@
         <v>9</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F41" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J41" s="13" t="s">
         <v>9</v>
@@ -10971,10 +11125,10 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>128</v>
@@ -10983,19 +11137,19 @@
         <v>9</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F42" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J42" s="13" t="s">
         <v>9</v>
@@ -11011,10 +11165,10 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>128</v>
@@ -11023,19 +11177,19 @@
         <v>9</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F43" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J43" s="13" t="s">
         <v>9</v>
@@ -11051,10 +11205,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>128</v>
@@ -11063,19 +11217,19 @@
         <v>9</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F44" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J44" s="13" t="s">
         <v>9</v>
@@ -11091,10 +11245,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
+        <v>637</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>639</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>128</v>
@@ -11103,19 +11257,19 @@
         <v>9</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F45" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J45" s="13" t="s">
         <v>9</v>
@@ -11131,10 +11285,10 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>644</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>645</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>128</v>
@@ -11143,19 +11297,19 @@
         <v>9</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F46" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J46" s="13" t="s">
         <v>9</v>
@@ -11171,10 +11325,10 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>128</v>
@@ -11183,19 +11337,19 @@
         <v>9</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F47" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J47" s="13" t="s">
         <v>9</v>
@@ -11211,10 +11365,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>128</v>
@@ -11223,19 +11377,19 @@
         <v>9</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F48" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H48" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J48" s="13" t="s">
         <v>9</v>
@@ -11251,10 +11405,10 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
+        <v>722</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>723</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>724</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>128</v>
@@ -11269,13 +11423,13 @@
         <v>20</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J49" s="13" t="s">
         <v>25</v>
@@ -11291,10 +11445,10 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
+        <v>742</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>743</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>744</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>128</v>
@@ -11303,19 +11457,19 @@
         <v>9</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F50" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J50" s="13" t="s">
         <v>9</v>
@@ -11331,10 +11485,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
+        <v>744</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>745</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>746</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>128</v>
@@ -11343,19 +11497,19 @@
         <v>9</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F51" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J51" s="13" t="s">
         <v>9</v>
@@ -11371,10 +11525,10 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
+        <v>748</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>749</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>750</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>128</v>
@@ -11383,19 +11537,19 @@
         <v>9</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F52" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H52" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J52" s="13" t="s">
         <v>9</v>
@@ -11411,10 +11565,10 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
+        <v>751</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>752</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>753</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>128</v>
@@ -11423,19 +11577,19 @@
         <v>9</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F53" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J53" s="13" t="s">
         <v>9</v>
@@ -11451,10 +11605,10 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
+        <v>780</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>781</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>782</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>128</v>
@@ -11463,19 +11617,19 @@
         <v>9</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F54" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H54" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J54" s="13" t="s">
         <v>9</v>
@@ -11491,10 +11645,10 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
+        <v>789</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>790</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>791</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>128</v>
@@ -11503,19 +11657,19 @@
         <v>9</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F55" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J55" s="13" t="s">
         <v>9</v>
@@ -11531,10 +11685,10 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
+        <v>792</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>793</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>794</v>
       </c>
       <c r="C56" s="13" t="s">
         <v>128</v>
@@ -11543,19 +11697,19 @@
         <v>9</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F56" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J56" s="13" t="s">
         <v>9</v>
@@ -11571,10 +11725,10 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
+        <v>804</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>805</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>806</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>128</v>
@@ -11583,19 +11737,19 @@
         <v>9</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F57" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J57" s="13" t="s">
         <v>9</v>
@@ -11611,10 +11765,10 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
+        <v>807</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>808</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>128</v>
@@ -11623,19 +11777,19 @@
         <v>9</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F58" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H58" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J58" s="13" t="s">
         <v>9</v>
@@ -11651,10 +11805,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
+        <v>823</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>824</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>825</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>128</v>
@@ -11663,19 +11817,19 @@
         <v>9</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F59" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H59" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J59" s="13" t="s">
         <v>9</v>
@@ -11691,10 +11845,10 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
+        <v>826</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>827</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>828</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>128</v>
@@ -11703,19 +11857,19 @@
         <v>9</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F60" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H60" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J60" s="13" t="s">
         <v>9</v>
@@ -11731,10 +11885,10 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
+        <v>837</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>838</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>839</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>128</v>
@@ -11743,19 +11897,19 @@
         <v>9</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F61" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H61" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J61" s="13" t="s">
         <v>9</v>
@@ -11771,10 +11925,10 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>128</v>
@@ -11783,19 +11937,19 @@
         <v>9</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F62" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H62" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J62" s="13" t="s">
         <v>9</v>
@@ -11811,10 +11965,10 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>128</v>
@@ -11823,19 +11977,19 @@
         <v>25</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F63" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H63" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J63" s="13" t="s">
         <v>25</v>
@@ -11851,10 +12005,10 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>128</v>
@@ -11863,19 +12017,19 @@
         <v>25</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F64" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H64" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J64" s="13" t="s">
         <v>25</v>
@@ -11891,10 +12045,10 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>128</v>
@@ -11903,19 +12057,19 @@
         <v>25</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F65" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H65" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J65" s="13" t="s">
         <v>25</v>
@@ -11931,10 +12085,10 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>128</v>
@@ -11943,19 +12097,19 @@
         <v>9</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F66" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H66" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J66" s="13" t="s">
         <v>9</v>
@@ -11971,10 +12125,10 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>128</v>
@@ -11983,19 +12137,19 @@
         <v>9</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F67" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H67" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J67" s="13" t="s">
         <v>9</v>
@@ -12011,10 +12165,10 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>128</v>
@@ -12023,19 +12177,19 @@
         <v>9</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F68" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H68" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J68" s="13" t="s">
         <v>9</v>
@@ -12051,10 +12205,10 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C69" s="13" t="s">
         <v>128</v>
@@ -12063,19 +12217,19 @@
         <v>9</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F69" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H69" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J69" s="13" t="s">
         <v>9</v>
@@ -12091,10 +12245,10 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>1037</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>1038</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>128</v>
@@ -12103,19 +12257,19 @@
         <v>9</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F70" s="23" t="s">
         <v>20</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H70" s="13" t="s">
         <v>129</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J70" s="13" t="s">
         <v>9</v>
@@ -12179,10 +12333,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1" s="13" t="s">
         <v>5</v>
@@ -12220,29 +12374,29 @@
         <v>345</v>
       </c>
       <c r="F2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>64</v>
       </c>
       <c r="L2" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I2 = "IND", "L-",I2 = "Ferrite", "F-"),A2)</f>
+        <f t="shared" ref="L2:L11" si="0">_xlfn.CONCAT(_xlfn.IFS(I2 = "IND", "L-",I2 = "Ferrite", "F-"),A2)</f>
         <v>L-0805LS-471XJEC</v>
       </c>
       <c r="M2" s="14" t="str">
-        <f t="shared" ref="M2:M11" si="0">L2</f>
+        <f t="shared" ref="M2:M11" si="1">L2</f>
         <v>L-0805LS-471XJEC</v>
       </c>
     </row>
@@ -12263,29 +12417,29 @@
         <v>344</v>
       </c>
       <c r="F3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="L3" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I3 = "IND", "L-",I3 = "Ferrite", "F-"),A3)</f>
+        <f t="shared" si="0"/>
         <v>L-0402FL-181XJRW</v>
       </c>
       <c r="M3" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>L-0402FL-181XJRW</v>
       </c>
     </row>
@@ -12306,29 +12460,29 @@
         <v>343</v>
       </c>
       <c r="F4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="L4" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I4 = "IND", "L-",I4 = "Ferrite", "F-"),A4)</f>
+        <f t="shared" si="0"/>
         <v>L-0402FL-360XJRW</v>
       </c>
       <c r="M4" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>L-0402FL-360XJRW</v>
       </c>
     </row>
@@ -12349,38 +12503,38 @@
         <v>348</v>
       </c>
       <c r="F5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="L5" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I5 = "IND", "L-",I5 = "Ferrite", "F-"),A5)</f>
+        <f t="shared" si="0"/>
         <v>L-0402FL-200XJRW</v>
       </c>
       <c r="M5" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>L-0402FL-200XJRW</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>80</v>
@@ -12389,41 +12543,41 @@
         <v>11</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F6" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="L6" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I6 = "IND", "L-",I6 = "Ferrite", "F-"),A6)</f>
+        <f t="shared" si="0"/>
         <v>L-LQW18AN10NG00</v>
       </c>
       <c r="M6" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>L-LQW18AN10NG00</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>922</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>923</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>194</v>
@@ -12432,41 +12586,41 @@
         <v>9</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F7" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="L7" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I7 = "IND", "L-",I7 = "Ferrite", "F-"),A7)</f>
+        <f t="shared" si="0"/>
         <v>L-0402CS-39NXGLW</v>
       </c>
       <c r="M7" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>L-0402CS-39NXGLW</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>80</v>
@@ -12475,41 +12629,41 @@
         <v>11</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F8" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="L8" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I8 = "IND", "L-",I8 = "Ferrite", "F-"),A8)</f>
+        <f t="shared" si="0"/>
         <v>L-LQW18AN18NG00D</v>
       </c>
       <c r="M8" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>L-LQW18AN18NG00D</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>80</v>
@@ -12518,41 +12672,41 @@
         <v>9</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F9" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="L9" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I9 = "IND", "L-",I9 = "Ferrite", "F-"),A9)</f>
+        <f t="shared" si="0"/>
         <v>L-LQW15AN18NG00D</v>
       </c>
       <c r="M9" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>L-LQW15AN18NG00D</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>194</v>
@@ -12561,41 +12715,41 @@
         <v>12</v>
       </c>
       <c r="E10" s="13" t="s">
+        <v>953</v>
+      </c>
+      <c r="F10" t="s">
+        <v>917</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="F10" t="s">
-        <v>918</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>955</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="L10" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I10 = "IND", "L-",I10 = "Ferrite", "F-"),A10)</f>
+        <f t="shared" si="0"/>
         <v>L-0805CS-030XJRC</v>
       </c>
       <c r="M10" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>L-0805CS-030XJRC</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
+        <v>969</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>970</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>971</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>80</v>
@@ -12604,32 +12758,32 @@
         <v>25</v>
       </c>
       <c r="E11" s="13" t="s">
+        <v>971</v>
+      </c>
+      <c r="F11" t="s">
+        <v>917</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>972</v>
       </c>
-      <c r="F11" t="s">
-        <v>918</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>973</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="L11" s="14" t="str">
-        <f>_xlfn.CONCAT(_xlfn.IFS(I11 = "IND", "L-",I11 = "Ferrite", "F-"),A11)</f>
+        <f t="shared" si="0"/>
         <v>L-LQP03HQ1N5C02D</v>
       </c>
       <c r="M11" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>L-LQP03HQ1N5C02D</v>
       </c>
     </row>
@@ -12644,7 +12798,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E51C6DE-D099-40FE-9416-B104F9965BCA}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="2" bestFit="1" customWidth="1"/>
@@ -12707,16 +12861,16 @@
         <v>205</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>206</v>
@@ -12744,26 +12898,26 @@
         <v>172</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>172</v>
       </c>
       <c r="J3" s="14" t="str">
-        <f t="shared" ref="J3:J10" si="0">_xlfn.CONCAT(_xlfn.IFS(G3 = "IND", "L-",G3 = "Ferrite", "F-"),A3)</f>
+        <f t="shared" ref="J3:J13" si="0">_xlfn.CONCAT(_xlfn.IFS(G3 = "IND", "L-",G3 = "Ferrite", "F-"),A3)</f>
         <v>L-IHLP2525CZER100M5A</v>
       </c>
       <c r="K3" s="14" t="str">
-        <f t="shared" ref="K3:K10" si="1">J3</f>
+        <f t="shared" ref="K3:K13" si="1">J3</f>
         <v>L-IHLP2525CZER100M5A</v>
       </c>
     </row>
@@ -12781,16 +12935,16 @@
         <v>424</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="J4" s="14" t="str">
         <f t="shared" si="0"/>
@@ -12815,16 +12969,16 @@
         <v>532</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="J5" s="14" t="str">
         <f t="shared" si="0"/>
@@ -12837,10 +12991,10 @@
     </row>
     <row r="6" spans="1:11" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>834</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>835</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>836</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>148</v>
@@ -12849,19 +13003,19 @@
         <v>328</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="J6" s="14" t="str">
         <f t="shared" si="0"/>
@@ -12889,13 +13043,13 @@
         <v>81</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>82</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>9</v>
@@ -12926,13 +13080,13 @@
         <v>81</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>82</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>11</v>
@@ -12948,10 +13102,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>940</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>941</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>80</v>
@@ -12960,16 +13114,16 @@
         <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>82</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>9</v>
@@ -12988,7 +13142,7 @@
         <v>74439324015</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>148</v>
@@ -13000,13 +13154,13 @@
         <v>533</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>13</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I10" s="2">
         <v>4030</v>
@@ -13020,7 +13174,119 @@
         <v>L-74439324015</v>
       </c>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>891</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="J11" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>L-IHLP2525CZER2R2M01</v>
+      </c>
+      <c r="K11" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>L-IHLP2525CZER2R2M01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>891</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>L-IHLP2525CZER4R7M01</v>
+      </c>
+      <c r="K12" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>L-IHLP2525CZER4R7M01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>891</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="J13" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>L-IHLP2525CZER1R0M01</v>
+      </c>
+      <c r="K13" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>L-IHLP2525CZER1R0M01</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13081,7 +13347,7 @@
         <v>80</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>514</v>
@@ -13108,7 +13374,7 @@
         <v>80</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>515</v>
@@ -13135,22 +13401,22 @@
         <v>80</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>82</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13164,22 +13430,22 @@
         <v>80</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>82</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
   </sheetData>
@@ -13256,22 +13522,22 @@
         <v>203</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>997</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>998</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>202</v>
       </c>
       <c r="J2" s="13" t="str">
-        <f>A2</f>
+        <f t="shared" ref="J2:J33" si="0">A2</f>
         <v>CWDT8005</v>
       </c>
       <c r="K2" s="2" t="str">
@@ -13293,7 +13559,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>45</v>
@@ -13302,17 +13568,17 @@
         <v>38</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>199</v>
       </c>
       <c r="J3" s="13" t="str">
-        <f>A3</f>
+        <f t="shared" si="0"/>
         <v>CWS23902</v>
       </c>
       <c r="K3" s="2" t="str">
-        <f t="shared" ref="K3:K12" si="0">J3</f>
+        <f t="shared" ref="K3:K12" si="1">J3</f>
         <v>CWS23902</v>
       </c>
       <c r="N3" s="34"/>
@@ -13331,26 +13597,26 @@
         <v>212</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>997</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>998</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>40</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I4" s="13" t="s">
         <v>213</v>
       </c>
       <c r="J4" s="13" t="str">
-        <f>A4</f>
+        <f t="shared" si="0"/>
         <v>IPA-0206B-CQ5B</v>
       </c>
       <c r="K4" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>IPA-0206B-CQ5B</v>
       </c>
       <c r="N4" s="35"/>
@@ -13369,26 +13635,26 @@
         <v>237</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>234</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>237</v>
       </c>
       <c r="J5" s="13" t="str">
-        <f>A5</f>
+        <f t="shared" si="0"/>
         <v>TRHJ-2041</v>
       </c>
       <c r="K5" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>TRHJ-2041</v>
       </c>
       <c r="N5" s="34"/>
@@ -13407,26 +13673,26 @@
         <v>240</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>241</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>240</v>
       </c>
       <c r="J6" s="13" t="str">
-        <f>A6</f>
+        <f t="shared" si="0"/>
         <v>ADF5356BCPZ</v>
       </c>
       <c r="K6" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>ADF5356BCPZ</v>
       </c>
       <c r="N6" s="35"/>
@@ -13445,26 +13711,26 @@
         <v>245</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>246</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>245</v>
       </c>
       <c r="J7" s="13" t="str">
-        <f>A7</f>
+        <f t="shared" si="0"/>
         <v>LFCG-2000+</v>
       </c>
       <c r="K7" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>LFCG-2000+</v>
       </c>
       <c r="N7" s="34"/>
@@ -13481,26 +13747,26 @@
         <v>254</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>253</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>254</v>
       </c>
       <c r="J8" s="13" t="str">
-        <f>A8</f>
+        <f t="shared" si="0"/>
         <v>LFCN-1500D+</v>
       </c>
       <c r="K8" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>LFCN-1500D+</v>
       </c>
       <c r="N8" s="35"/>
@@ -13516,26 +13782,26 @@
         <v>258</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>257</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>255</v>
       </c>
       <c r="J9" s="13" t="str">
-        <f>A9</f>
+        <f t="shared" si="0"/>
         <v>CWNPA-2735-P40-M</v>
       </c>
       <c r="K9" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>CWNPA-2735-P40-M</v>
       </c>
       <c r="N9" s="34"/>
@@ -13554,26 +13820,26 @@
         <v>261</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>259</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>262</v>
       </c>
       <c r="J10" s="13" t="str">
-        <f>A10</f>
+        <f t="shared" si="0"/>
         <v>TSY-83LN+</v>
       </c>
       <c r="K10" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>TSY-83LN+</v>
       </c>
       <c r="N10" s="35"/>
@@ -13592,26 +13858,26 @@
         <v>295</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>293</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>296</v>
       </c>
       <c r="J11" s="13" t="str">
-        <f>A11</f>
+        <f t="shared" si="0"/>
         <v>TSY-173LN+</v>
       </c>
       <c r="K11" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>TSY-173LN+</v>
       </c>
       <c r="N11" s="34"/>
@@ -13630,26 +13896,26 @@
         <v>296</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>299</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>296</v>
       </c>
       <c r="J12" s="13" t="str">
-        <f>A12</f>
+        <f t="shared" si="0"/>
         <v>YAT-10A+</v>
       </c>
       <c r="K12" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>YAT-10A+</v>
       </c>
       <c r="N12" s="35"/>
@@ -13668,26 +13934,26 @@
         <v>296</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>299</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>296</v>
       </c>
       <c r="J13" s="13" t="str">
-        <f>A13</f>
+        <f t="shared" si="0"/>
         <v>YAT-6A+</v>
       </c>
       <c r="K13" s="2" t="str">
-        <f t="shared" ref="K13:K24" si="1">J13</f>
+        <f t="shared" ref="K13:K24" si="2">J13</f>
         <v>YAT-6A+</v>
       </c>
       <c r="N13" s="34"/>
@@ -13697,7 +13963,7 @@
         <v>314</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>100</v>
@@ -13706,26 +13972,26 @@
         <v>315</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>314</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>340</v>
       </c>
       <c r="J14" s="13" t="str">
-        <f>A14</f>
+        <f t="shared" si="0"/>
         <v>LMX2594RHA</v>
       </c>
       <c r="K14" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>LMX2594RHA</v>
       </c>
       <c r="N14" s="35"/>
@@ -13744,26 +14010,26 @@
         <v>381</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>379</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>381</v>
       </c>
       <c r="J15" s="13" t="str">
-        <f>A15</f>
+        <f t="shared" si="0"/>
         <v>SMIQ-6243H+</v>
       </c>
       <c r="K15" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>SMIQ-6243H+</v>
       </c>
       <c r="N15" s="34"/>
@@ -13782,26 +14048,26 @@
         <v>381</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>382</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>381</v>
       </c>
       <c r="J16" s="13" t="str">
-        <f>A16</f>
+        <f t="shared" si="0"/>
         <v>EP2C+</v>
       </c>
       <c r="K16" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>EP2C+</v>
       </c>
       <c r="N16" s="35"/>
@@ -13820,26 +14086,26 @@
         <v>384</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>385</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>384</v>
       </c>
       <c r="J17" s="13" t="str">
-        <f>A17</f>
+        <f t="shared" si="0"/>
         <v>EP2RCW+</v>
       </c>
       <c r="K17" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>EP2RCW+</v>
       </c>
       <c r="N17" s="34"/>
@@ -13858,26 +14124,26 @@
         <v>389</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>253</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>389</v>
       </c>
       <c r="J18" s="13" t="str">
-        <f>A18</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">LFCW-8700+ </v>
       </c>
       <c r="K18" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">LFCW-8700+ </v>
       </c>
       <c r="N18" s="35"/>
@@ -13896,26 +14162,26 @@
         <v>1008</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>393</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>393</v>
       </c>
       <c r="J19" s="13" t="str">
-        <f>A19</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">3350BP39A0500001E </v>
       </c>
       <c r="K19" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">3350BP39A0500001E </v>
       </c>
       <c r="N19" s="34"/>
@@ -13934,26 +14200,26 @@
         <v>395</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>395</v>
       </c>
       <c r="J20" s="13" t="str">
-        <f>A20</f>
+        <f t="shared" si="0"/>
         <v>QCN-45+</v>
       </c>
       <c r="K20" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>QCN-45+</v>
       </c>
       <c r="N20" s="35"/>
@@ -13972,26 +14238,26 @@
         <v>400</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>1017</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>1018</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>397</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>400</v>
       </c>
       <c r="J21" s="13" t="str">
-        <f>A21</f>
+        <f t="shared" si="0"/>
         <v>SKY13575-639LF</v>
       </c>
       <c r="K21" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>SKY13575-639LF</v>
       </c>
       <c r="N21" s="34"/>
@@ -14010,34 +14276,34 @@
         <v>445</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="13" t="str">
-        <f>A22</f>
+        <f t="shared" si="0"/>
         <v>ADRV9026BBCZ</v>
       </c>
       <c r="K22" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>ADRV9026BBCZ</v>
       </c>
       <c r="N22" s="35"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>91</v>
@@ -14046,34 +14312,34 @@
         <v>431</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13" t="str">
-        <f>A23</f>
+        <f t="shared" si="0"/>
         <v>HMC451LP3</v>
       </c>
       <c r="K23" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>HMC451LP3</v>
       </c>
       <c r="N23" s="34"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
+        <v>673</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>674</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>675</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>244</v>
@@ -14082,31 +14348,31 @@
         <v>261</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13" t="str">
-        <f>A24</f>
+        <f t="shared" si="0"/>
         <v>AVA-183P+</v>
       </c>
       <c r="K24" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>AVA-183P+</v>
       </c>
       <c r="N24" s="35"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>298</v>
@@ -14118,33 +14384,33 @@
         <v>296</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>299</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>296</v>
       </c>
       <c r="J25" s="13" t="str">
-        <f>A25</f>
+        <f t="shared" si="0"/>
         <v>YAT-0A+</v>
       </c>
       <c r="K25" s="2" t="str">
-        <f t="shared" ref="K25:K29" si="2">J25</f>
+        <f t="shared" ref="K25:K29" si="3">J25</f>
         <v>YAT-0A+</v>
       </c>
       <c r="N25" s="34"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>394</v>
@@ -14153,36 +14419,36 @@
         <v>244</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G26" s="13" t="s">
+        <v>676</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="I26" s="13" t="s">
         <v>677</v>
       </c>
-      <c r="H26" s="13" t="s">
-        <v>888</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>678</v>
-      </c>
       <c r="J26" s="13" t="str">
-        <f>A26</f>
+        <f t="shared" si="0"/>
         <v>EP2KA+</v>
       </c>
       <c r="K26" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>EP2KA+</v>
       </c>
       <c r="N26" s="35"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>298</v>
@@ -14194,33 +14460,33 @@
         <v>296</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>299</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>296</v>
       </c>
       <c r="J27" s="13" t="str">
-        <f>A27</f>
+        <f t="shared" si="0"/>
         <v>YAT-3A+</v>
       </c>
       <c r="K27" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>YAT-3A+</v>
       </c>
       <c r="N27" s="34"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>444</v>
@@ -14232,278 +14498,278 @@
         <v>445</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="13" t="str">
-        <f>A28</f>
+        <f t="shared" si="0"/>
         <v>ADRV9025BBCZ</v>
       </c>
       <c r="K28" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>ADRV9025BBCZ</v>
       </c>
       <c r="N28" s="35"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>689</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>690</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>227</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13" t="str">
-        <f>A29</f>
+        <f t="shared" si="0"/>
         <v>CWS13102</v>
       </c>
       <c r="K29" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>CWS13102</v>
       </c>
       <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>692</v>
-      </c>
       <c r="C30" s="13" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>227</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I30" s="13"/>
       <c r="J30" s="13" t="str">
-        <f>A30</f>
+        <f t="shared" si="0"/>
         <v>CWS13101</v>
       </c>
       <c r="K30" s="2" t="str">
-        <f t="shared" ref="K30:K34" si="3">J30</f>
+        <f t="shared" ref="K30:K34" si="4">J30</f>
         <v>CWS13101</v>
       </c>
       <c r="N30" s="35"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
+        <v>694</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>695</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="C31" s="13" t="s">
         <v>696</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>697</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>510</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="J31" s="13" t="str">
-        <f>A31</f>
+        <f t="shared" si="0"/>
         <v>QPA1008</v>
       </c>
       <c r="K31" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>QPA1008</v>
       </c>
       <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
+        <v>697</v>
+      </c>
+      <c r="B32" s="13" t="s">
         <v>698</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>699</v>
-      </c>
       <c r="C32" s="13" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>122</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J32" s="13" t="str">
-        <f>A32</f>
+        <f t="shared" si="0"/>
         <v>TQL9092</v>
       </c>
       <c r="K32" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>TQL9092</v>
       </c>
       <c r="N32" s="35"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="B33" s="29" t="s">
         <v>700</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>701</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>392</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I33" s="13"/>
       <c r="J33" s="13" t="str">
-        <f>A33</f>
+        <f t="shared" si="0"/>
         <v>4400BL15A0100E</v>
       </c>
       <c r="K33" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4400BL15A0100E</v>
       </c>
       <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
+        <v>702</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>703</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>704</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I34" s="13"/>
       <c r="J34" s="13" t="str">
-        <f>A34</f>
+        <f t="shared" ref="J34:J53" si="5">A34</f>
         <v>D17W+</v>
       </c>
       <c r="K34" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>D17W+</v>
       </c>
       <c r="N34" s="35"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
+        <v>705</v>
+      </c>
+      <c r="B35" s="27" t="s">
         <v>706</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>707</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E35" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>1017</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>1018</v>
-      </c>
       <c r="G35" s="13" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="J35" s="13" t="str">
-        <f>A35</f>
+        <f t="shared" si="5"/>
         <v>HMC544A</v>
       </c>
       <c r="K35" s="2" t="str">
@@ -14514,34 +14780,34 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>775</v>
-      </c>
       <c r="H36" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="J36" s="13" t="str">
-        <f>A36</f>
+        <f t="shared" si="5"/>
         <v>ADMV1014ACCZ</v>
       </c>
       <c r="K36" s="2" t="str">
@@ -14552,34 +14818,34 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
+        <v>776</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>777</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>778</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D37" s="13" t="s">
+        <v>778</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>780</v>
-      </c>
       <c r="H37" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="J37" s="13" t="str">
-        <f>A37</f>
+        <f t="shared" si="5"/>
         <v>ADMV1013ACCZ</v>
       </c>
       <c r="K37" s="2" t="str">
@@ -14590,34 +14856,34 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
+        <v>795</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>797</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D38" s="13" t="s">
+        <v>797</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G38" s="13" t="s">
         <v>798</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>799</v>
-      </c>
       <c r="H38" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J38" s="13" t="str">
-        <f>A38</f>
+        <f t="shared" si="5"/>
         <v>ADRF5024BCCZN</v>
       </c>
       <c r="K38" s="2" t="str">
@@ -14628,7 +14894,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>394</v>
@@ -14637,39 +14903,39 @@
         <v>244</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G39" s="13" t="s">
         <v>801</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>802</v>
-      </c>
       <c r="H39" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="J39" s="13" t="str">
-        <f>A39</f>
+        <f t="shared" si="5"/>
         <v>QCS-83+</v>
       </c>
       <c r="K39" s="2" t="str">
-        <f t="shared" ref="K39:K40" si="4">J39</f>
+        <f t="shared" ref="K39:K40" si="6">J39</f>
         <v>QCS-83+</v>
       </c>
       <c r="N39" s="34"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
+        <v>802</v>
+      </c>
+      <c r="B40" s="13" t="s">
         <v>803</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>804</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>244</v>
@@ -14678,60 +14944,60 @@
         <v>384</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="J40" s="13" t="str">
-        <f>A40</f>
+        <f t="shared" si="5"/>
         <v>EP4RKU+</v>
       </c>
       <c r="K40" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>EP4RKU+</v>
       </c>
       <c r="N40" s="35"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="J41" s="13" t="str">
-        <f>A41</f>
+        <f t="shared" si="5"/>
         <v>GVA-93+</v>
       </c>
       <c r="K41" s="2" t="str">
@@ -14742,10 +15008,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>817</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>818</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>244</v>
@@ -14754,22 +15020,22 @@
         <v>261</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I42" s="13" t="s">
         <v>261</v>
       </c>
       <c r="J42" s="13" t="str">
-        <f>A42</f>
+        <f t="shared" si="5"/>
         <v>PMA3-83LN+</v>
       </c>
       <c r="K42" s="2" t="str">
@@ -14780,10 +15046,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
+        <v>818</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>820</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>244</v>
@@ -14792,22 +15058,22 @@
         <v>389</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>253</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>389</v>
       </c>
       <c r="J43" s="13" t="str">
-        <f>A43</f>
+        <f t="shared" si="5"/>
         <v>BFCW-542+</v>
       </c>
       <c r="K43" s="2" t="str">
@@ -14818,38 +15084,38 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>236</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>823</v>
-      </c>
       <c r="H44" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="J44" s="13" t="str">
-        <f>A44</f>
+        <f t="shared" si="5"/>
         <v>TRHJ-4061</v>
       </c>
       <c r="K44" s="2" t="str">
-        <f t="shared" ref="K44:K50" si="5">J44</f>
+        <f t="shared" ref="K44:K50" si="7">J44</f>
         <v>TRHJ-4061</v>
       </c>
       <c r="N44" s="35"/>
@@ -14868,74 +15134,74 @@
         <v>227</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>225</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>228</v>
       </c>
       <c r="J45" s="13" t="str">
-        <f>A45</f>
-        <v>LTC5548</v>
-      </c>
-      <c r="K45" s="2" t="str">
         <f t="shared" si="5"/>
         <v>LTC5548</v>
       </c>
+      <c r="K45" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>LTC5548</v>
+      </c>
       <c r="N45" s="34"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B46" s="13" t="s">
         <v>937</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>938</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J46" s="13" t="str">
-        <f>A46</f>
-        <v>LHA-1+</v>
-      </c>
-      <c r="K46" s="2" t="str">
         <f t="shared" si="5"/>
         <v>LHA-1+</v>
       </c>
+      <c r="K46" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>LHA-1+</v>
+      </c>
       <c r="N46" s="35"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B47" s="13" t="s">
         <v>943</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>944</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>244</v>
@@ -14944,112 +15210,112 @@
         <v>254</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>253</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>254</v>
       </c>
       <c r="J47" s="13" t="str">
-        <f>A47</f>
-        <v>LFCN-5500D+</v>
-      </c>
-      <c r="K47" s="2" t="str">
         <f t="shared" si="5"/>
         <v>LFCN-5500D+</v>
       </c>
+      <c r="K47" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>LFCN-5500D+</v>
+      </c>
       <c r="N47" s="34"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B48" s="13" t="s">
         <v>945</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>946</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G48" s="13" t="s">
         <v>947</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G48" s="13" t="s">
-        <v>948</v>
-      </c>
       <c r="H48" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="J48" s="13" t="str">
-        <f>A48</f>
-        <v>HFCW-9500+</v>
-      </c>
-      <c r="K48" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HFCW-9500+</v>
       </c>
+      <c r="K48" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>HFCW-9500+</v>
+      </c>
       <c r="N48" s="35"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G49" s="13" t="s">
+        <v>948</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="I49" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="H49" s="13" t="s">
-        <v>888</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>950</v>
-      </c>
       <c r="J49" s="13" t="str">
-        <f>A49</f>
-        <v>AVA-183A+</v>
-      </c>
-      <c r="K49" s="2" t="str">
         <f t="shared" si="5"/>
         <v>AVA-183A+</v>
       </c>
+      <c r="K49" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>AVA-183A+</v>
+      </c>
       <c r="N49" s="34"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="B50" s="13" t="s">
         <v>964</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>965</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>244</v>
@@ -15058,36 +15324,36 @@
         <v>395</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>395</v>
       </c>
       <c r="J50" s="13" t="str">
-        <f>A50</f>
-        <v>HFCN-7150+</v>
-      </c>
-      <c r="K50" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HFCN-7150+</v>
       </c>
+      <c r="K50" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>HFCN-7150+</v>
+      </c>
       <c r="N50" s="35"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>91</v>
@@ -15096,74 +15362,74 @@
         <v>227</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>228</v>
       </c>
       <c r="J51" s="13" t="str">
-        <f>A51</f>
+        <f t="shared" si="5"/>
         <v>LTC5553</v>
       </c>
       <c r="K51" s="2" t="str">
-        <f t="shared" ref="K51:K53" si="6">J51</f>
+        <f t="shared" ref="K51:K53" si="8">J51</f>
         <v>LTC5553</v>
       </c>
       <c r="N51" s="34"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
+        <v>974</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>975</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>976</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G52" s="13" t="s">
         <v>947</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G52" s="13" t="s">
-        <v>948</v>
-      </c>
       <c r="H52" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="J52" s="13" t="str">
-        <f>A52</f>
+        <f t="shared" si="5"/>
         <v>HFCW-1132+</v>
       </c>
       <c r="K52" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>HFCW-1132+</v>
       </c>
       <c r="N52" s="35"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>991</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>992</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>244</v>
@@ -15172,212 +15438,212 @@
         <v>381</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>381</v>
       </c>
       <c r="J53" s="13" t="str">
-        <f>A53</f>
+        <f t="shared" si="5"/>
         <v>EP2K+</v>
       </c>
       <c r="K53" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>EP2K+</v>
       </c>
       <c r="N53" s="34"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>995</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>996</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D54" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="E54" s="13" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>995</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>888</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>1016</v>
-      </c>
       <c r="J54" s="13" t="str">
-        <f t="shared" ref="J54:J58" si="7">A54</f>
+        <f t="shared" ref="J54:J58" si="9">A54</f>
         <v>ADRF5238</v>
       </c>
       <c r="K54" s="2" t="str">
-        <f t="shared" ref="K54:K58" si="8">J54</f>
+        <f t="shared" ref="K54:K58" si="10">J54</f>
         <v>ADRF5238</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>253</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="J55" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>BFCN-3700+</v>
       </c>
       <c r="K55" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>BFCN-3700+</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>1023</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>1024</v>
       </c>
       <c r="C56" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="J56" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>BFHKI-9901+</v>
       </c>
       <c r="K56" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>BFHKI-9901+</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G57" s="13" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="I57" s="13" t="s">
         <v>1026</v>
       </c>
-      <c r="H57" s="13" t="s">
-        <v>888</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>1027</v>
-      </c>
       <c r="J57" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>AVA-6183MPS+</v>
       </c>
       <c r="K57" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>AVA-6183MPS+</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>244</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="J58" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>PMA2-183LN+</v>
       </c>
       <c r="K58" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>PMA2-183LN+</v>
       </c>
     </row>
@@ -15465,24 +15731,24 @@
         <v>51</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="2" t="str">
-        <f t="shared" ref="J2:J14" si="0">_xlfn.CONCAT("X-",A2)</f>
-        <v>X-142-0761-801</v>
+      <c r="J2" s="13" t="str">
+        <f>A2</f>
+        <v>142-0761-801</v>
       </c>
       <c r="K2" s="14" t="str">
-        <f t="shared" ref="K2:K22" si="1">J2</f>
-        <v>X-142-0761-801</v>
+        <f t="shared" ref="K2:K24" si="0">J2</f>
+        <v>142-0761-801</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15499,24 +15765,24 @@
         <v>74</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>72</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="J3" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>X-53398-0471</v>
+      <c r="J3" s="13" t="str">
+        <f t="shared" ref="J3:J24" si="1">A3</f>
+        <v>53398-0471</v>
       </c>
       <c r="K3" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>X-53398-0471</v>
+        <f t="shared" si="0"/>
+        <v>53398-0471</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15533,24 +15799,24 @@
         <v>74</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>76</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I4" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="J4" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>X-87832-1420</v>
+      <c r="J4" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>87832-1420</v>
       </c>
       <c r="K4" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>X-87832-1420</v>
+        <f t="shared" si="0"/>
+        <v>87832-1420</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15570,24 +15836,24 @@
         <v>494</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="J5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>X-85305-0232</v>
+      <c r="J5" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>85305-0232</v>
       </c>
       <c r="K5" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>X-85305-0232</v>
+        <f t="shared" si="0"/>
+        <v>85305-0232</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15607,24 +15873,24 @@
         <v>51</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="J6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>X-SMA-KYHDC</v>
+      <c r="J6" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>SMA-KYHDC</v>
       </c>
       <c r="K6" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>X-SMA-KYHDC</v>
+        <f t="shared" si="0"/>
+        <v>SMA-KYHDC</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15635,30 +15901,30 @@
         <v>289</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>290</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>288</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="J7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>X-TB006-508-02BE</v>
+      <c r="J7" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>TB006-508-02BE</v>
       </c>
       <c r="K7" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>X-TB006-508-02BE</v>
+        <f t="shared" si="0"/>
+        <v>TB006-508-02BE</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15675,24 +15941,24 @@
         <v>74</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>356</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="J8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>X-S2B-ZR-SM4A-TF</v>
+      <c r="J8" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>S2B-ZR-SM4A-TF</v>
       </c>
       <c r="K8" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>X-S2B-ZR-SM4A-TF</v>
+        <f t="shared" si="0"/>
+        <v>S2B-ZR-SM4A-TF</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15709,21 +15975,21 @@
         <v>452</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>449</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>897</v>
-      </c>
-      <c r="J9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>X-SOLC-120-02-F-Q-A-K-TR</v>
+        <v>896</v>
+      </c>
+      <c r="J9" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>SOLC-120-02-F-Q-A-K-TR</v>
       </c>
       <c r="K9" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>X-SOLC-120-02-F-Q-A-K-TR</v>
+        <f t="shared" si="0"/>
+        <v>SOLC-120-02-F-Q-A-K-TR</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15743,24 +16009,24 @@
         <v>492</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>489</v>
       </c>
       <c r="J10" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>X-SMP-MSLD-PCT-6</v>
+        <f t="shared" si="1"/>
+        <v>SMP-MSLD-PCT-6</v>
       </c>
       <c r="K10" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-SMP-MSLD-PCT-6</v>
+        <f t="shared" si="0"/>
+        <v>SMP-MSLD-PCT-6</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15780,24 +16046,24 @@
         <v>494</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>495</v>
       </c>
       <c r="J11" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>X-SMP-MSSB-PCS</v>
+        <f t="shared" si="1"/>
+        <v>SMP-MSSB-PCS</v>
       </c>
       <c r="K11" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-SMP-MSSB-PCS</v>
+        <f t="shared" si="0"/>
+        <v>SMP-MSSB-PCS</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15814,21 +16080,21 @@
         <v>502</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>500</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J12" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>X-47352-1001</v>
+        <f t="shared" si="1"/>
+        <v>47352-1001</v>
       </c>
       <c r="K12" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-47352-1001</v>
+        <f t="shared" si="0"/>
+        <v>47352-1001</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15845,21 +16111,21 @@
         <v>521</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>518</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J13" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>X-PJ-002B</v>
+        <f t="shared" si="1"/>
+        <v>PJ-002B</v>
       </c>
       <c r="K13" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-PJ-002B</v>
+        <f t="shared" si="0"/>
+        <v>PJ-002B</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15876,267 +16142,337 @@
         <v>572</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>569</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J14" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>X-ZX62R-B-5P</v>
+        <f t="shared" si="1"/>
+        <v>ZX62R-B-5P</v>
       </c>
       <c r="K14" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-ZX62R-B-5P</v>
+        <f t="shared" si="0"/>
+        <v>ZX62R-B-5P</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>583</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>582</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G15" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>584</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>583</v>
-      </c>
-      <c r="F15" s="13" t="s">
+      <c r="H15" s="13" t="s">
         <v>896</v>
       </c>
-      <c r="G15" s="16" t="s">
-        <v>586</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>897</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>582</v>
+      <c r="J15" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>ADM6-60-01.5-L-4-2-A-TR_1</v>
       </c>
       <c r="K15" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>ADM6-60-01.5-L-4-2-A-TR</v>
+        <f t="shared" si="0"/>
+        <v>ADM6-60-01.5-L-4-2-A-TR_1</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F16" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>896</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>897</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>582</v>
+      <c r="J16" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>ADM6-60-01.5-L-4-2-A-TR_2</v>
       </c>
       <c r="K16" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>ADM6-60-01.5-L-4-2-A-TR</v>
+        <f t="shared" si="0"/>
+        <v>ADM6-60-01.5-L-4-2-A-TR_2</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>635</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>636</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>423</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F17" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="H17" s="13" t="s">
         <v>896</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>635</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>897</v>
-      </c>
       <c r="J17" s="13" t="str">
-        <f t="shared" ref="J17:J22" si="2">_xlfn.CONCAT("X-",A17)</f>
-        <v>X-J0G-0001NL</v>
+        <f t="shared" si="1"/>
+        <v>J0G-0001NL</v>
       </c>
       <c r="K17" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-J0G-0001NL</v>
+        <f t="shared" si="0"/>
+        <v>J0G-0001NL</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>654</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>653</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="D18" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>654</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>656</v>
-      </c>
       <c r="F18" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>896</v>
       </c>
-      <c r="G18" s="13" t="s">
-        <v>653</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>897</v>
-      </c>
       <c r="J18" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>X-20021321-00050T4LF</v>
+        <f t="shared" si="1"/>
+        <v>20021321-00050T4LF</v>
       </c>
       <c r="K18" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-20021321-00050T4LF</v>
+        <f t="shared" si="0"/>
+        <v>20021321-00050T4LF</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B19" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>657</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
+        <v>897</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>658</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>898</v>
-      </c>
-      <c r="F19" s="13" t="s">
+      <c r="H19" s="13" t="s">
         <v>896</v>
       </c>
-      <c r="G19" s="13" t="s">
-        <v>659</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>897</v>
-      </c>
       <c r="J19" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>X-2199119-2</v>
+        <f t="shared" si="1"/>
+        <v>2199119-2</v>
       </c>
       <c r="K19" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-2199119-2</v>
+        <f t="shared" si="0"/>
+        <v>2199119-2</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
+        <v>663</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>664</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="C20" s="13" t="s">
         <v>665</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="13" t="s">
         <v>666</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="F20" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="H20" s="13" t="s">
         <v>896</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>668</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>897</v>
-      </c>
       <c r="J20" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>X-15EDGRC-3.81-06P-14-00A(H)</v>
+        <f t="shared" si="1"/>
+        <v>15EDGRC-3.81-06P-14-00A(H)</v>
       </c>
       <c r="K20" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-15EDGRC-3.81-06P-14-00A(H)</v>
+        <f t="shared" si="0"/>
+        <v>15EDGRC-3.81-06P-14-00A(H)</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
+        <v>713</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>714</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>715</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>148</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F21" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>713</v>
+      </c>
+      <c r="H21" s="13" t="s">
         <v>896</v>
       </c>
-      <c r="G21" s="13" t="s">
-        <v>714</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>897</v>
-      </c>
       <c r="J21" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>X-61202021621</v>
+        <f t="shared" si="1"/>
+        <v>61202021621</v>
       </c>
       <c r="K21" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>X-61202021621</v>
+        <f t="shared" si="0"/>
+        <v>61202021621</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>717</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>718</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>491</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F22" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="H22" s="13" t="s">
         <v>896</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>717</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>897</v>
-      </c>
       <c r="J22" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>X-G14A421211112HR</v>
+        <f t="shared" si="1"/>
+        <v>G14A421211112HR</v>
       </c>
       <c r="K22" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>G14A421211112HR</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>896</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="J23" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>X-G14A421211112HR</v>
+        <v>G14A42221612AHR</v>
+      </c>
+      <c r="K23" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>G14A42221612AHR</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>896</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>1048</v>
+      </c>
+      <c r="J24" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>1586037-4</v>
+      </c>
+      <c r="K24" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>1586037-4</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">

--- a/Altium-library.xlsx
+++ b/Altium-library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Altium-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDBF7BC-F39C-4C32-B8CE-9C1E29141D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366EEEB6-0BC4-4CF1-A071-A32ADF8E8AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="771" firstSheet="1" activeTab="10" xr2:uid="{C01531D5-0FFE-4276-86E2-3D80C8EFC4F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="771" firstSheet="1" activeTab="8" xr2:uid="{C01531D5-0FFE-4276-86E2-3D80C8EFC4F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Capacitors_General" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2987" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2999" uniqueCount="1065">
   <si>
     <t>Part Number</t>
   </si>
@@ -3239,6 +3239,15 @@
   </si>
   <si>
     <t>Керамическая антенна на S_Band</t>
+  </si>
+  <si>
+    <t>RT0603BRD07100KL</t>
+  </si>
+  <si>
+    <t>100kΩ ±1% 0.1W 0603 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>LQPF-64</t>
   </si>
 </sst>
 </file>
@@ -7072,6 +7081,9 @@
       <c r="G5" s="2" t="s">
         <v>887</v>
       </c>
+      <c r="H5" s="2" t="s">
+        <v>1064</v>
+      </c>
       <c r="I5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>FT4232HL</v>
@@ -9467,7 +9479,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237531C5-FF99-4DE6-90F6-D20DBFB61F6B}">
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
@@ -12155,11 +12167,11 @@
         <v>9</v>
       </c>
       <c r="K67" s="14" t="str">
-        <f t="shared" ref="K67:K70" si="38">_xlfn.CONCAT("R-", D67,"-",E67," ",_xlfn.IFS(F67 ="±0,1", "B", F67 = "±0,25", "C", F67 = "±0,5", "D", F67 = "±1%", "F",F67="±2%","G",F67="±5%", "J", F67="±10%", "K", F67="±20%", "M"))</f>
+        <f t="shared" ref="K67:K71" si="38">_xlfn.CONCAT("R-", D67,"-",E67," ",_xlfn.IFS(F67 ="±0,1", "B", F67 = "±0,25", "C", F67 = "±0,5", "D", F67 = "±1%", "F",F67="±2%","G",F67="±5%", "J", F67="±10%", "K", F67="±20%", "M"))</f>
         <v>R-0402-11K8 F</v>
       </c>
       <c r="L67" s="13" t="str">
-        <f t="shared" ref="L67:L70" si="39">K67</f>
+        <f t="shared" ref="L67:L71" si="39">K67</f>
         <v>R-0402-11K8 F</v>
       </c>
     </row>
@@ -12281,6 +12293,46 @@
       <c r="L70" s="13" t="str">
         <f t="shared" si="39"/>
         <v>R-0402-270K F</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F71" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>889</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>888</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="K71" s="14" t="str">
+        <f t="shared" si="38"/>
+        <v>R-0603-100K F</v>
+      </c>
+      <c r="L71" s="13" t="str">
+        <f t="shared" si="39"/>
+        <v>R-0603-100K F</v>
       </c>
     </row>
   </sheetData>
@@ -16119,6 +16171,9 @@
       <c r="H13" s="13" t="s">
         <v>896</v>
       </c>
+      <c r="I13" s="13" t="s">
+        <v>518</v>
+      </c>
       <c r="J13" s="13" t="str">
         <f t="shared" si="1"/>
         <v>PJ-002B</v>

--- a/Altium-library.xlsx
+++ b/Altium-library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Altium-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED4687F-F887-410E-B681-61AF61605F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1D668B-3699-4997-84C8-C027BBABB565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="771" firstSheet="2" activeTab="8" xr2:uid="{C01531D5-0FFE-4276-86E2-3D80C8EFC4F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="771" firstSheet="1" activeTab="3" xr2:uid="{C01531D5-0FFE-4276-86E2-3D80C8EFC4F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Capacitors_General" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3528" uniqueCount="1279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3735" uniqueCount="1341">
   <si>
     <t>Part Number</t>
   </si>
@@ -3894,6 +3894,192 @@
   </si>
   <si>
     <t>ADM6-60-01.5-L-4-2-A-TR</t>
+  </si>
+  <si>
+    <t>LTC5549</t>
+  </si>
+  <si>
+    <t>2GHz to 14GHz Microwave Mixer with Wideband DC–6GHz Diff-IF</t>
+  </si>
+  <si>
+    <t>XLF-662M+</t>
+  </si>
+  <si>
+    <t>XHF-63M+</t>
+  </si>
+  <si>
+    <t>XHF-73M+</t>
+  </si>
+  <si>
+    <t>XLF-132H+</t>
+  </si>
+  <si>
+    <t>MNA-4A+</t>
+  </si>
+  <si>
+    <t>TA0332A</t>
+  </si>
+  <si>
+    <t>PVGA-123+</t>
+  </si>
+  <si>
+    <t>BFHKI-8501+</t>
+  </si>
+  <si>
+    <t>PMA3-5123+</t>
+  </si>
+  <si>
+    <t>B070MB6S</t>
+  </si>
+  <si>
+    <t>PSA-14+</t>
+  </si>
+  <si>
+    <t>Reflectionless Low Pass Filter, DC - 6000 MHz, 50Ω</t>
+  </si>
+  <si>
+    <t>LPF_12</t>
+  </si>
+  <si>
+    <t>Reflectionless High Pass Filter, 5900 - 19000 MHz, 50Ω</t>
+  </si>
+  <si>
+    <t>HPF_12</t>
+  </si>
+  <si>
+    <t>Reflectionless High Pass Filter, 7000 - 16400 MHz</t>
+  </si>
+  <si>
+    <t>Reflectionless Low Pass Filter, DC - 1300 MHz, 50Ω</t>
+  </si>
+  <si>
+    <t>LPF_24</t>
+  </si>
+  <si>
+    <t>SMT MMIC, Medium Power, Linear, pHEMT Amplifier, 500 MHz to 2500 MHz, 50Ω, 3x3 mm QFN Style Package</t>
+  </si>
+  <si>
+    <t>SAW Filter 1350MHz SMD 3.0×3.0mm</t>
+  </si>
+  <si>
+    <t>TAI-SAW TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>SMD_6</t>
+  </si>
+  <si>
+    <t>SMT MMIC, Medium Power, Linear, Variable Gain, HBT Amplifier, 400 MHz to 12 GHz, 50Ω, 3x3 mm QFN Style Package</t>
+  </si>
+  <si>
+    <t>LTCC SMT Band Pass Filter, 7.5 - 8.8 GHz, 50Ω</t>
+  </si>
+  <si>
+    <t>SMT Low Noise Amplifier, 5.5 - 12.5 GHz, 50Ω</t>
+  </si>
+  <si>
+    <t>DQ3005</t>
+  </si>
+  <si>
+    <t>7.10GHz Surface Mount Bandpass Filter</t>
+  </si>
+  <si>
+    <t>Knowles</t>
+  </si>
+  <si>
+    <t>12.7*5.08</t>
+  </si>
+  <si>
+    <t>SMT MMIC, Linear, Gain Block, HBT, Low Phase Noise Amplifier, 10 MHz to 10 GHz, 50Ω, SOT-343 Style Package</t>
+  </si>
+  <si>
+    <t>MMM1362</t>
+  </si>
+  <si>
+    <t>FPC06073</t>
+  </si>
+  <si>
+    <t>ADL5519</t>
+  </si>
+  <si>
+    <t>ADPA1120</t>
+  </si>
+  <si>
+    <t>4.5W (36.5dBm), 8GHz to 12GHz, GaN Power Amplifier</t>
+  </si>
+  <si>
+    <t>4 to 8GHz 10dB Directional Coupler</t>
+  </si>
+  <si>
+    <t>4.3 x 2.0</t>
+  </si>
+  <si>
+    <t>1 MHz TO 10 GHz, 62 dB Dual Log Detector / Controller</t>
+  </si>
+  <si>
+    <t>RC0805FR-0733RL</t>
+  </si>
+  <si>
+    <t>33Ω ±1% 0.125W 0805 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>RC0402FR-073K92L</t>
+  </si>
+  <si>
+    <t>3.92kΩ ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>3K92</t>
+  </si>
+  <si>
+    <t>RC0402FR-079K53L</t>
+  </si>
+  <si>
+    <t>9.53kΩ ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>9K53</t>
+  </si>
+  <si>
+    <t>RC0402FR-075K11L</t>
+  </si>
+  <si>
+    <t>5K11</t>
+  </si>
+  <si>
+    <t>5.11kΩ ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>RC0402FR-078K45L</t>
+  </si>
+  <si>
+    <t>8.45kΩ ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>8K45</t>
+  </si>
+  <si>
+    <t>YAT-30A+</t>
+  </si>
+  <si>
+    <t>INA293A2</t>
+  </si>
+  <si>
+    <t>INA293 –4 V to 110 V, 1.3-MHz, Ultra-Precise Current Sense Amplifier</t>
+  </si>
+  <si>
+    <t>INA293</t>
+  </si>
+  <si>
+    <t>WSL1206R0500FTB</t>
+  </si>
+  <si>
+    <t>Current Sense Resistors - SMD 1/4watt .05ohms 1%</t>
+  </si>
+  <si>
+    <t>1206</t>
+  </si>
+  <si>
+    <t>0R05</t>
   </si>
 </sst>
 </file>
@@ -4164,6 +4350,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4203,7 +4390,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4766,8 +4952,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BA8796F4-0E9A-4FD9-96F0-8E2E1FAFB6A1}" name="Таблица5" displayName="Таблица5" ref="A1:L93" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
-  <autoFilter ref="A1:L93" xr:uid="{BA8796F4-0E9A-4FD9-96F0-8E2E1FAFB6A1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BA8796F4-0E9A-4FD9-96F0-8E2E1FAFB6A1}" name="Таблица5" displayName="Таблица5" ref="A1:L99" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+  <autoFilter ref="A1:L99" xr:uid="{BA8796F4-0E9A-4FD9-96F0-8E2E1FAFB6A1}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{4E47D3E6-A38E-40F5-83F3-40F1076D2958}" name="Part Number" dataDxfId="63"/>
     <tableColumn id="2" xr3:uid="{198BEEE1-E92F-4E81-98C4-A397E0824233}" name="Description" dataDxfId="62"/>
@@ -4841,8 +5027,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1FD5FABE-37A7-40DD-B0BB-8B0C0B397C06}" name="Таблица1" displayName="Таблица1" ref="A1:K63" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
-  <autoFilter ref="A1:K63" xr:uid="{1FD5FABE-37A7-40DD-B0BB-8B0C0B397C06}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1FD5FABE-37A7-40DD-B0BB-8B0C0B397C06}" name="Таблица1" displayName="Таблица1" ref="A1:K79" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+  <autoFilter ref="A1:K79" xr:uid="{1FD5FABE-37A7-40DD-B0BB-8B0C0B397C06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K60">
     <sortCondition ref="E1:E60"/>
   </sortState>
@@ -4864,22 +5050,22 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{228D11DC-D3B4-41B0-9E6D-16E577335585}" name="Таблица9" displayName="Таблица9" ref="A1:K26" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{228D11DC-D3B4-41B0-9E6D-16E577335585}" name="Таблица9" displayName="Таблица9" ref="A1:K26" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:K26" xr:uid="{228D11DC-D3B4-41B0-9E6D-16E577335585}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{6AB3B5DB-5FE8-4A84-9A31-9FA7BCAF98EE}" name="Part Number" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{1F7D06E6-3D96-4783-8A48-CEE6A0E7884C}" name="Description" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{B11ABE86-E927-4C53-BF75-9C432F06AD18}" name="Manufacturer" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{891E6F7B-8883-4743-9C04-CB3302BEB2F1}" name="Type" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{822A977A-21C0-46D3-B0FE-11D4E63E17EA}" name="FREQ" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{FDAA4013-11CA-4B4F-AE3C-D8F0AA99AC41}" name="Library Path" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{A6578727-6C98-48ED-9249-A487F5A6387C}" name="Library Ref" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{BFF2F226-8DC7-4C2D-B801-CBB276C1AB46}" name="Footprint Path 1" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{6806AFCF-5C93-4313-87FD-554D0A75122B}" name="Footprint Ref 1" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{D0BA53E9-9171-4B74-9CBA-1789479BDF06}" name="UID" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{6AB3B5DB-5FE8-4A84-9A31-9FA7BCAF98EE}" name="Part Number" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{1F7D06E6-3D96-4783-8A48-CEE6A0E7884C}" name="Description" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{B11ABE86-E927-4C53-BF75-9C432F06AD18}" name="Manufacturer" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{891E6F7B-8883-4743-9C04-CB3302BEB2F1}" name="Type" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{822A977A-21C0-46D3-B0FE-11D4E63E17EA}" name="FREQ" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{FDAA4013-11CA-4B4F-AE3C-D8F0AA99AC41}" name="Library Path" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{A6578727-6C98-48ED-9249-A487F5A6387C}" name="Library Ref" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{BFF2F226-8DC7-4C2D-B801-CBB276C1AB46}" name="Footprint Path 1" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{6806AFCF-5C93-4313-87FD-554D0A75122B}" name="Footprint Ref 1" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{D0BA53E9-9171-4B74-9CBA-1789479BDF06}" name="UID" dataDxfId="1">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{9206910B-9B13-40E0-B075-8ED883C959D1}" name="PnP_name" dataDxfId="2">
+    <tableColumn id="11" xr3:uid="{9206910B-9B13-40E0-B075-8ED883C959D1}" name="PnP_name" dataDxfId="0">
       <calculatedColumnFormula>J2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8466,7 +8652,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0C0C3AA-8F1E-4D93-8E4C-115E6E30BA7E}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.25" style="2" customWidth="1"/>
@@ -8742,11 +8928,11 @@
         <v>869</v>
       </c>
       <c r="J8" s="2" t="str">
-        <f t="shared" ref="J8:J11" si="2">A8</f>
+        <f t="shared" ref="J8:J12" si="2">A8</f>
         <v>ASGTX-C-120.00MHZ-1</v>
       </c>
       <c r="K8" s="2" t="str">
-        <f t="shared" ref="K8:K11" si="3">J8</f>
+        <f t="shared" ref="K8:K12" si="3">J8</f>
         <v>ASGTX-C-120.00MHZ-1</v>
       </c>
     </row>
@@ -8856,6 +9042,43 @@
       <c r="K11" s="2" t="str">
         <f t="shared" si="3"/>
         <v>ADA4930-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="J12" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>INA293A2</v>
+      </c>
+      <c r="K12" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>INA293A2</v>
       </c>
     </row>
   </sheetData>
@@ -12326,7 +12549,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237531C5-FF99-4DE6-90F6-D20DBFB61F6B}">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
@@ -16109,7 +16332,7 @@
         <v>R-0402-4K7 F</v>
       </c>
       <c r="L92" s="12" t="str">
-        <f t="shared" ref="L92:L93" si="73">K92</f>
+        <f t="shared" ref="L92:L94" si="73">K92</f>
         <v>R-0402-4K7 F</v>
       </c>
     </row>
@@ -16152,6 +16375,252 @@
       <c r="L93" s="12" t="str">
         <f t="shared" si="73"/>
         <v>R-0402-90K9 B</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="F94" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="H94" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I94" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="J94" s="13" t="str">
+        <f>_xlfn.CONCAT("R",D94)</f>
+        <v>R0805</v>
+      </c>
+      <c r="K94" s="13" t="str">
+        <f t="shared" ref="K94:K95" si="74">_xlfn.CONCAT("R-", D94,"-",E94," ",_xlfn.IFS(F94 ="±0,1", "B", F94 = "±0,25", "C", F94 = "±0,5", "D", F94 = "±1%", "F",F94="±2%","G",F94="±5%", "J", F94="±10%", "K", F94="±20%", "M"))</f>
+        <v>R-0805-33R F</v>
+      </c>
+      <c r="L94" s="12" t="str">
+        <f t="shared" si="73"/>
+        <v>R-0805-33R F</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F95" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="H95" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I95" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="J95" s="13" t="str">
+        <f t="shared" ref="J95" si="75">_xlfn.CONCAT("R",D95)</f>
+        <v>R0402</v>
+      </c>
+      <c r="K95" s="13" t="str">
+        <f t="shared" si="74"/>
+        <v>R-0402-3K92 F</v>
+      </c>
+      <c r="L95" s="12" t="str">
+        <f t="shared" ref="L95" si="76">K95</f>
+        <v>R-0402-3K92 F</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F96" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="H96" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="J96" s="13" t="str">
+        <f t="shared" ref="J96" si="77">_xlfn.CONCAT("R",D96)</f>
+        <v>R0402</v>
+      </c>
+      <c r="K96" s="13" t="str">
+        <f t="shared" ref="K96" si="78">_xlfn.CONCAT("R-", D96,"-",E96," ",_xlfn.IFS(F96 ="±0,1", "B", F96 = "±0,25", "C", F96 = "±0,5", "D", F96 = "±1%", "F",F96="±2%","G",F96="±5%", "J", F96="±10%", "K", F96="±20%", "M"))</f>
+        <v>R-0402-9K53 F</v>
+      </c>
+      <c r="L96" s="12" t="str">
+        <f t="shared" ref="L96" si="79">K96</f>
+        <v>R-0402-9K53 F</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F97" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="H97" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I97" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="J97" s="13" t="str">
+        <f t="shared" ref="J97" si="80">_xlfn.CONCAT("R",D97)</f>
+        <v>R0402</v>
+      </c>
+      <c r="K97" s="13" t="str">
+        <f t="shared" ref="K97" si="81">_xlfn.CONCAT("R-", D97,"-",E97," ",_xlfn.IFS(F97 ="±0,1", "B", F97 = "±0,25", "C", F97 = "±0,5", "D", F97 = "±1%", "F",F97="±2%","G",F97="±5%", "J", F97="±10%", "K", F97="±20%", "M"))</f>
+        <v>R-0402-5K11 F</v>
+      </c>
+      <c r="L97" s="12" t="str">
+        <f t="shared" ref="L97" si="82">K97</f>
+        <v>R-0402-5K11 F</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F98" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="H98" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I98" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="J98" s="13" t="str">
+        <f t="shared" ref="J98" si="83">_xlfn.CONCAT("R",D98)</f>
+        <v>R0402</v>
+      </c>
+      <c r="K98" s="13" t="str">
+        <f t="shared" ref="K98:K99" si="84">_xlfn.CONCAT("R-", D98,"-",E98," ",_xlfn.IFS(F98 ="±0,1", "B", F98 = "±0,25", "C", F98 = "±0,5", "D", F98 = "±1%", "F",F98="±2%","G",F98="±5%", "J", F98="±10%", "K", F98="±20%", "M"))</f>
+        <v>R-0402-8K45 F</v>
+      </c>
+      <c r="L98" s="12" t="str">
+        <f t="shared" ref="L98" si="85">K98</f>
+        <v>R-0402-8K45 F</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" s="12" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F99" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="H99" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I99" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="J99" s="13" t="str">
+        <f>_xlfn.CONCAT("R",D99)</f>
+        <v>R1206</v>
+      </c>
+      <c r="K99" s="13" t="str">
+        <f t="shared" si="84"/>
+        <v>R-1206-0R05 F</v>
+      </c>
+      <c r="L99" s="12" t="str">
+        <f>K99</f>
+        <v>R-1206-0R05 F</v>
       </c>
     </row>
   </sheetData>
@@ -17588,7 +18057,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{714F4FB9-2DCB-4869-B7AF-00FC94C1C3DC}">
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" style="12" customWidth="1"/>
@@ -17600,7 +18069,8 @@
     <col min="7" max="7" width="18.375" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="21.75" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.125" style="2" customWidth="1"/>
-    <col min="11" max="12" width="11" style="2"/>
+    <col min="11" max="11" width="25.125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2"/>
     <col min="13" max="13" width="8.75" style="2" customWidth="1"/>
     <col min="14" max="16384" width="11" style="2"/>
   </cols>
@@ -19627,8 +20097,8 @@
         <f t="shared" si="2"/>
         <v>ADRF5019BCPZN</v>
       </c>
-      <c r="K55" s="2" t="str">
-        <f t="shared" si="3"/>
+      <c r="K55" s="12" t="str">
+        <f>J55</f>
         <v>ADRF5019BCPZN</v>
       </c>
     </row>
@@ -19928,11 +20398,598 @@
         <v>HFCN-2700AD+</v>
       </c>
     </row>
-    <row r="79" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H64" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="J64" s="12" t="str">
+        <f t="shared" ref="J64:J78" si="6">A64</f>
+        <v>LTC5549</v>
+      </c>
+      <c r="K64" s="2" t="str">
+        <f t="shared" ref="K64:K78" si="7">J64</f>
+        <v>LTC5549</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H65" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="J65" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>XLF-662M+</v>
+      </c>
+      <c r="K65" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>XLF-662M+</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H66" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="J66" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>XHF-63M+</v>
+      </c>
+      <c r="K66" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>XHF-63M+</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="J67" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>XHF-73M+</v>
+      </c>
+      <c r="K67" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>XHF-73M+</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H68" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="J68" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>XLF-132H+</v>
+      </c>
+      <c r="K68" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>XLF-132H+</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>929</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H69" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>929</v>
+      </c>
+      <c r="J69" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>MNA-4A+</v>
+      </c>
+      <c r="K69" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>MNA-4A+</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H70" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I70" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J70" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>TA0332A</v>
+      </c>
+      <c r="K70" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>TA0332A</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="J71" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>PVGA-123+</v>
+      </c>
+      <c r="K71" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>PVGA-123+</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H72" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J72" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>BFHKI-8501+</v>
+      </c>
+      <c r="K72" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>BFHKI-8501+</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H73" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J73" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>PMA3-5123+</v>
+      </c>
+      <c r="K73" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>PMA3-5123+</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J74" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>B070MB6S</v>
+      </c>
+      <c r="K74" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>B070MB6S</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J75" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>PSA-14+</v>
+      </c>
+      <c r="K75" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>PSA-14+</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>1317</v>
+      </c>
+      <c r="J76" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>FPC06073</v>
+      </c>
+      <c r="K76" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>FPC06073</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H77" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="J77" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>ADL5519</v>
+      </c>
+      <c r="K77" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>ADL5519</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="J78" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>ADPA1120</v>
+      </c>
+      <c r="K78" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>ADPA1120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="12" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>990</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="J79" s="12" t="str">
+        <f>A79</f>
+        <v>YAT-30A+</v>
+      </c>
+      <c r="K79" s="2" t="str">
+        <f>J79</f>
+        <v>YAT-30A+</v>
+      </c>
       <c r="M79" s="33"/>
-    </row>
-    <row r="80" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M80" s="33"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
